--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-01T08:29:46+00:00</t>
+    <t>2024-07-19T01:11:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T01:11:55+00:00</t>
+    <t>2024-07-19T01:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T01:26:25+00:00</t>
+    <t>2024-07-19T02:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T02:29:01+00:00</t>
+    <t>2024-07-19T05:36:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T05:36:29+00:00</t>
+    <t>2024-07-19T06:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T06:18:24+00:00</t>
+    <t>2024-07-20T07:34:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-20T07:34:22+00:00</t>
+    <t>2024-07-20T10:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
